--- a/thisisnotthedroidyouarelookingfor/situacoes_placas.xlsx
+++ b/thisisnotthedroidyouarelookingfor/situacoes_placas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -406,50 +406,24 @@
       <c r="B1" t="str">
         <v>Situacao</v>
       </c>
+      <c r="C1" t="str">
+        <v>Data de criacao</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>OPZ4G70</v>
+        <v>QQY4F99</v>
       </c>
       <c r="B2" t="str">
-        <v>Concluída</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>QMT7J41</v>
-      </c>
-      <c r="B3" t="str">
         <v>Pendente</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>TDO8D16</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Pendente</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>RWV6H65</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Agendada</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>GFS4C62</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Pendente</v>
+      <c r="C2" t="str">
+        <v>10/09/2026 12:29</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>